--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D411C5EB-2405-4D29-A452-837CC4A2DC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CEAD31-2C0C-4F58-9A93-CEE1EF3D5587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6915" yWindow="-13860" windowWidth="14535" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionEffectData" sheetId="1" r:id="rId1"/>
@@ -441,7 +441,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E2" s="2">
         <v>0</v>

--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -1,31 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CEAD31-2C0C-4F58-9A93-CEE1EF3D5587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1085B1E6-CFB8-4FFD-8D02-80821B6B2649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionEffectData" sheetId="1" r:id="rId1"/>
+    <sheet name="reference" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -50,6 +60,73 @@
     <rPh sb="4" eb="6">
       <t>コウカ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力依存のダメージ</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>固定値のHP回復</t>
+    <rPh sb="0" eb="2">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>固定値の満腹度回復</t>
+    <rPh sb="0" eb="2">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>マンプク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>固定ダメージ</t>
+    <rPh sb="0" eb="2">
+      <t>コテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムを焼く</t>
+    <rPh sb="5" eb="6">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムを腐らせる</t>
+    <rPh sb="5" eb="6">
+      <t>クサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>select</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -73,7 +150,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -89,6 +166,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -120,11 +203,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -405,15 +489,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -424,27 +509,110 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="4">
+        <f>VLOOKUP(D2,reference!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2">
         <v>100</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="2">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7E37C01A-20C3-4913-9C61-3425DDA6962E}">
+          <x14:formula1>
+            <xm:f>reference!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9D75E7-07CD-4EC3-B8C1-A3DF3DE98F1D}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1085B1E6-CFB8-4FFD-8D02-80821B6B2649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF778E5F-78B6-43E7-8F0D-85A36F334AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF778E5F-78B6-43E7-8F0D-85A36F334AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908CA19E-369B-4637-97BE-5D0F395EE2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -127,6 +127,62 @@
   </si>
   <si>
     <t>select</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力%</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未使用</t>
+    <rPh sb="0" eb="3">
+      <t>ミシヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回復量</t>
+    <rPh sb="0" eb="3">
+      <t>カイフクリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメージ量</t>
+    <rPh sb="4" eb="5">
+      <t>リョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HP1回復</t>
+    <rPh sb="3" eb="5">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HP20回復</t>
+    <rPh sb="4" eb="6">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>満腹度30回復</t>
+    <rPh sb="0" eb="3">
+      <t>マンプクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>満腹度100回復</t>
+    <rPh sb="0" eb="3">
+      <t>マンプクド</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -489,16 +545,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,8 +575,14 @@
       <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -537,6 +601,130 @@
       </c>
       <c r="F2" s="2">
         <v>0</v>
+      </c>
+      <c r="G2" s="4" t="str">
+        <f>VLOOKUP(D2,reference!A:D,3,FALSE)</f>
+        <v>攻撃力%</v>
+      </c>
+      <c r="H2" s="4" t="str">
+        <f>VLOOKUP(D2,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4">
+        <f>VLOOKUP(D3,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="str">
+        <f>VLOOKUP(D3,reference!A:D,3,FALSE)</f>
+        <v>回復量</v>
+      </c>
+      <c r="H3" s="4" t="str">
+        <f>VLOOKUP(D3,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4">
+        <f>VLOOKUP(D4,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2">
+        <v>20</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="str">
+        <f>VLOOKUP(D4,reference!A:D,3,FALSE)</f>
+        <v>回復量</v>
+      </c>
+      <c r="H4" s="4" t="str">
+        <f>VLOOKUP(D4,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="4">
+        <f>VLOOKUP(D5,reference!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2">
+        <v>30</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="str">
+        <f>VLOOKUP(D5,reference!A:D,3,FALSE)</f>
+        <v>回復量</v>
+      </c>
+      <c r="H5" s="4" t="str">
+        <f>VLOOKUP(D5,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="4">
+        <f>VLOOKUP(D6,reference!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2">
+        <v>100</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="str">
+        <f>VLOOKUP(D6,reference!A:D,3,FALSE)</f>
+        <v>回復量</v>
+      </c>
+      <c r="H6" s="4" t="str">
+        <f>VLOOKUP(D6,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
       </c>
     </row>
   </sheetData>
@@ -550,7 +738,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>D2</xm:sqref>
+          <xm:sqref>D2:D6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -560,46 +748,71 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9D75E7-07CD-4EC3-B8C1-A3DF3DE98F1D}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="21.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>5</v>
       </c>
       <c r="B1">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -607,7 +820,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>10</v>
       </c>

--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908CA19E-369B-4637-97BE-5D0F395EE2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E760B78F-0D3B-4012-9780-B16CC37EA579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3885" yWindow="-14010" windowWidth="16995" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionEffectData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -182,6 +182,13 @@
     <t>満腹度100回復</t>
     <rPh sb="0" eb="3">
       <t>マンプクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>固定5ダメージ</t>
+    <rPh sb="0" eb="2">
+      <t>コテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -545,11 +552,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="21.125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="8.375" bestFit="1" customWidth="1"/>
@@ -724,6 +731,93 @@
       </c>
       <c r="H6" s="4" t="str">
         <f>VLOOKUP(D6,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4">
+        <f>VLOOKUP(D7,reference!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="str">
+        <f>VLOOKUP(D7,reference!A:D,3,FALSE)</f>
+        <v>未使用</v>
+      </c>
+      <c r="H7" s="4" t="str">
+        <f>VLOOKUP(D7,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4">
+        <f>VLOOKUP(D8,reference!A:B,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="str">
+        <f>VLOOKUP(D8,reference!A:D,3,FALSE)</f>
+        <v>未使用</v>
+      </c>
+      <c r="H8" s="4" t="str">
+        <f>VLOOKUP(D8,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="4">
+        <f>VLOOKUP(D9,reference!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="str">
+        <f>VLOOKUP(D9,reference!A:D,3,FALSE)</f>
+        <v>ダメージ量</v>
+      </c>
+      <c r="H9" s="4" t="str">
+        <f>VLOOKUP(D9,reference!A:D,4,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
@@ -738,7 +832,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D6</xm:sqref>
+          <xm:sqref>D2:D9</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -819,6 +913,12 @@
       <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
@@ -826,6 +926,12 @@
       </c>
       <c r="B6">
         <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\2DRoguelikeAlfa\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E760B78F-0D3B-4012-9780-B16CC37EA579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA2705C-0952-4969-8FF8-83BEBAE29E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3885" yWindow="-14010" windowWidth="16995" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionEffectData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -189,6 +189,13 @@
     <t>固定5ダメージ</t>
     <rPh sb="0" eb="2">
       <t>コテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>場所替え</t>
+    <rPh sb="0" eb="3">
+      <t>バショガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -552,12 +559,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="8.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.625" bestFit="1" customWidth="1"/>
@@ -818,6 +825,35 @@
       </c>
       <c r="H9" s="4" t="str">
         <f>VLOOKUP(D9,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="4">
+        <f>VLOOKUP(D10,reference!A:B,2,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="str">
+        <f>VLOOKUP(D10,reference!A:D,3,FALSE)</f>
+        <v>未使用</v>
+      </c>
+      <c r="H10" s="4" t="str">
+        <f>VLOOKUP(D10,reference!A:D,4,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
@@ -832,7 +868,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D9</xm:sqref>
+          <xm:sqref>D2:D10</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -842,7 +878,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9D75E7-07CD-4EC3-B8C1-A3DF3DE98F1D}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="21.125" bestFit="1" customWidth="1"/>
@@ -934,6 +970,20 @@
         <v>13</v>
       </c>
     </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
